--- a/retail/rpoc/assets/files/9 .JB YAP BROTHERS FOOD SDN BHD - JULY'25.xlsx
+++ b/retail/rpoc/assets/files/9 .JB YAP BROTHERS FOOD SDN BHD - JULY'25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\Desktop\SEPT PROFIT LISTING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286B9648-A96E-47DE-9A9C-4EB78F6CDD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E31E87-7C05-4781-AA25-524E41707823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="588" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="588" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25-11590" sheetId="12" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="108">
   <si>
     <t>Tian Ma Group Holdings Pte Ltd</t>
   </si>
@@ -166,9 +166,6 @@
   </si>
   <si>
     <t>48</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>1 for $2.50
@@ -2233,6 +2230,54 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2323,52 +2368,94 @@
     <xf numFmtId="168" fontId="9" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="2" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2408,96 +2495,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4346,50 +4343,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="32.450000000000003" customHeight="1">
-      <c r="A1" s="243" t="s">
+      <c r="A1" s="213" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="244"/>
-      <c r="C1" s="244"/>
-      <c r="D1" s="244"/>
-      <c r="E1" s="244"/>
-      <c r="F1" s="244"/>
-      <c r="G1" s="244"/>
-      <c r="H1" s="244"/>
-      <c r="I1" s="244"/>
-      <c r="J1" s="244"/>
-      <c r="K1" s="244"/>
-      <c r="L1" s="244"/>
-      <c r="M1" s="244"/>
-      <c r="N1" s="244"/>
-      <c r="O1" s="245"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
+      <c r="M1" s="214"/>
+      <c r="N1" s="214"/>
+      <c r="O1" s="215"/>
       <c r="P1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="246" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" s="246"/>
+      <c r="Q1" s="216" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" s="216"/>
       <c r="S1" s="51"/>
     </row>
     <row r="2" spans="1:19" ht="31.7" customHeight="1" thickBot="1">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="217" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="M2" s="248"/>
-      <c r="N2" s="248"/>
-      <c r="O2" s="249"/>
+      <c r="B2" s="218"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="219"/>
       <c r="P2" s="16" t="s">
         <v>2</v>
       </c>
@@ -4417,37 +4414,37 @@
       <c r="M3" s="26"/>
       <c r="N3" s="27"/>
       <c r="O3" s="26"/>
-      <c r="P3" s="250" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q3" s="251"/>
-      <c r="R3" s="251"/>
-      <c r="S3" s="252"/>
+      <c r="P3" s="220" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="221"/>
+      <c r="R3" s="221"/>
+      <c r="S3" s="222"/>
     </row>
     <row r="4" spans="1:19" ht="22.7" customHeight="1" thickBot="1">
-      <c r="A4" s="253" t="s">
+      <c r="A4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="254"/>
-      <c r="C4" s="254"/>
-      <c r="D4" s="254"/>
-      <c r="E4" s="254"/>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="255"/>
+      <c r="B4" s="224"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="224"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="224"/>
+      <c r="G4" s="224"/>
+      <c r="H4" s="225"/>
       <c r="I4" s="53"/>
-      <c r="J4" s="256" t="s">
+      <c r="J4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
-      <c r="M4" s="257"/>
-      <c r="N4" s="257"/>
-      <c r="O4" s="257"/>
-      <c r="P4" s="257"/>
-      <c r="Q4" s="257"/>
-      <c r="R4" s="257"/>
-      <c r="S4" s="258"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="M4" s="227"/>
+      <c r="N4" s="227"/>
+      <c r="O4" s="227"/>
+      <c r="P4" s="227"/>
+      <c r="Q4" s="227"/>
+      <c r="R4" s="227"/>
+      <c r="S4" s="228"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="21"/>
@@ -4503,7 +4500,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M6" s="64" t="s">
         <v>29</v>
@@ -4528,16 +4525,16 @@
       </c>
     </row>
     <row r="68" spans="1:19" ht="48" customHeight="1" thickBot="1">
-      <c r="A68" s="223"/>
-      <c r="B68" s="224"/>
-      <c r="C68" s="224"/>
-      <c r="D68" s="225"/>
+      <c r="A68" s="239"/>
+      <c r="B68" s="240"/>
+      <c r="C68" s="240"/>
+      <c r="D68" s="241"/>
       <c r="E68" s="93"/>
       <c r="F68" s="125"/>
-      <c r="G68" s="233" t="s">
+      <c r="G68" s="249" t="s">
         <v>15</v>
       </c>
-      <c r="H68" s="235">
+      <c r="H68" s="251">
         <f>SUM([1]Sheet3!H306:H366)</f>
         <v>113452.4</v>
       </c>
@@ -4549,34 +4546,34 @@
         <f>SUM([1]Sheet3!K314:K366)</f>
         <v>30864.464831804271</v>
       </c>
-      <c r="L68" s="237" t="s">
+      <c r="L68" s="253" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="238"/>
-      <c r="N68" s="239">
+      <c r="M68" s="254"/>
+      <c r="N68" s="255">
         <f>SUM([1]Sheet3!O314:O366)</f>
         <v>55517.599999999999</v>
       </c>
-      <c r="O68" s="240"/>
-      <c r="P68" s="218" t="s">
+      <c r="O68" s="256"/>
+      <c r="P68" s="234" t="s">
         <v>18</v>
       </c>
-      <c r="Q68" s="219"/>
-      <c r="R68" s="241">
+      <c r="Q68" s="235"/>
+      <c r="R68" s="257">
         <f>N68-K71</f>
         <v>21373.813576494438</v>
       </c>
       <c r="S68" s="97"/>
     </row>
     <row r="69" spans="1:19" ht="48" customHeight="1" thickBot="1">
-      <c r="A69" s="226"/>
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
-      <c r="D69" s="225"/>
+      <c r="A69" s="242"/>
+      <c r="B69" s="240"/>
+      <c r="C69" s="240"/>
+      <c r="D69" s="241"/>
       <c r="E69" s="93"/>
       <c r="F69" s="126"/>
-      <c r="G69" s="234"/>
-      <c r="H69" s="236"/>
+      <c r="G69" s="250"/>
+      <c r="H69" s="252"/>
       <c r="I69" s="98"/>
       <c r="J69" s="99" t="s">
         <v>33</v>
@@ -4585,20 +4582,20 @@
         <f>K68*0.09</f>
         <v>2777.8018348623841</v>
       </c>
-      <c r="L69" s="213"/>
-      <c r="M69" s="213"/>
-      <c r="N69" s="213"/>
-      <c r="O69" s="213"/>
-      <c r="P69" s="220"/>
-      <c r="Q69" s="221"/>
-      <c r="R69" s="242"/>
+      <c r="L69" s="229"/>
+      <c r="M69" s="229"/>
+      <c r="N69" s="229"/>
+      <c r="O69" s="229"/>
+      <c r="P69" s="236"/>
+      <c r="Q69" s="237"/>
+      <c r="R69" s="258"/>
       <c r="S69" s="101"/>
     </row>
     <row r="70" spans="1:19" ht="70.5" thickBot="1">
-      <c r="A70" s="227"/>
-      <c r="B70" s="228"/>
-      <c r="C70" s="228"/>
-      <c r="D70" s="229"/>
+      <c r="A70" s="243"/>
+      <c r="B70" s="244"/>
+      <c r="C70" s="244"/>
+      <c r="D70" s="245"/>
       <c r="E70" s="102"/>
       <c r="F70" s="127"/>
       <c r="G70" s="103" t="s">
@@ -4615,14 +4612,14 @@
         <f>1650/3.29</f>
         <v>501.51975683890578</v>
       </c>
-      <c r="L70" s="213"/>
-      <c r="M70" s="213"/>
-      <c r="N70" s="213"/>
-      <c r="O70" s="213"/>
-      <c r="P70" s="214" t="s">
+      <c r="L70" s="229"/>
+      <c r="M70" s="229"/>
+      <c r="N70" s="229"/>
+      <c r="O70" s="229"/>
+      <c r="P70" s="230" t="s">
         <v>21</v>
       </c>
-      <c r="Q70" s="215"/>
+      <c r="Q70" s="231"/>
       <c r="R70" s="107">
         <f>R68/N68</f>
         <v>0.38499167068631279</v>
@@ -4630,10 +4627,10 @@
       <c r="S70" s="108"/>
     </row>
     <row r="71" spans="1:19" ht="93.75" thickBot="1">
-      <c r="A71" s="230"/>
-      <c r="B71" s="231"/>
-      <c r="C71" s="231"/>
-      <c r="D71" s="232"/>
+      <c r="A71" s="246"/>
+      <c r="B71" s="247"/>
+      <c r="C71" s="247"/>
+      <c r="D71" s="248"/>
       <c r="E71" s="109"/>
       <c r="F71" s="128"/>
       <c r="G71" s="110" t="s">
@@ -4654,11 +4651,11 @@
       <c r="L71" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="M71" s="216">
+      <c r="M71" s="232">
         <f>K70/K68</f>
         <v>1.624909939543533E-2</v>
       </c>
-      <c r="N71" s="217"/>
+      <c r="N71" s="233"/>
       <c r="O71" s="115"/>
       <c r="P71" s="24"/>
       <c r="Q71" s="24"/>
@@ -4682,14 +4679,14 @@
     </row>
     <row r="77" spans="1:19" s="117" customFormat="1">
       <c r="A77" s="117" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F77" s="130"/>
       <c r="N77" s="118"/>
     </row>
-    <row r="78" spans="1:19" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A78" s="222" t="s">
-        <v>52</v>
+    <row r="78" spans="1:19" s="238" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A78" s="238" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:19" s="117" customFormat="1">
@@ -4705,12 +4702,6 @@
   </sheetData>
   <autoFilter ref="A6:T71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="17">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="J4:S4"/>
     <mergeCell ref="L69:O70"/>
     <mergeCell ref="P70:Q70"/>
     <mergeCell ref="M71:N71"/>
@@ -4722,6 +4713,12 @@
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="N68:O68"/>
     <mergeCell ref="R68:R69"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="J4:S4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4738,10 +4735,10 @@
     <col min="2" max="2" width="65.28515625" style="47" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="2.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" bestFit="1" customWidth="1"/>
@@ -4757,50 +4754,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" ht="32.450000000000003" customHeight="1">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="289" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
-      <c r="O1" s="261"/>
+      <c r="B1" s="290"/>
+      <c r="C1" s="290"/>
+      <c r="D1" s="290"/>
+      <c r="E1" s="290"/>
+      <c r="F1" s="290"/>
+      <c r="G1" s="290"/>
+      <c r="H1" s="290"/>
+      <c r="I1" s="290"/>
+      <c r="J1" s="290"/>
+      <c r="K1" s="290"/>
+      <c r="L1" s="290"/>
+      <c r="M1" s="290"/>
+      <c r="N1" s="290"/>
+      <c r="O1" s="291"/>
       <c r="P1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="262">
+      <c r="Q1" s="292">
         <v>45738</v>
       </c>
-      <c r="R1" s="262"/>
+      <c r="R1" s="292"/>
       <c r="S1" s="44"/>
     </row>
     <row r="2" spans="1:20" s="20" customFormat="1" ht="31.7" customHeight="1" thickBot="1">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="217" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="M2" s="248"/>
-      <c r="N2" s="248"/>
-      <c r="O2" s="249"/>
+      <c r="B2" s="218"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="219"/>
       <c r="P2" s="16" t="s">
         <v>2</v>
       </c>
@@ -4828,37 +4825,37 @@
       <c r="M3" s="26"/>
       <c r="N3" s="27"/>
       <c r="O3" s="26"/>
-      <c r="P3" s="263" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q3" s="264"/>
-      <c r="R3" s="264"/>
-      <c r="S3" s="265"/>
+      <c r="P3" s="293" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q3" s="294"/>
+      <c r="R3" s="294"/>
+      <c r="S3" s="295"/>
     </row>
     <row r="4" spans="1:20" s="29" customFormat="1" ht="22.7" customHeight="1" thickBot="1">
-      <c r="A4" s="266" t="s">
+      <c r="A4" s="296" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="267"/>
-      <c r="C4" s="267"/>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="268"/>
+      <c r="B4" s="297"/>
+      <c r="C4" s="297"/>
+      <c r="D4" s="297"/>
+      <c r="E4" s="297"/>
+      <c r="F4" s="297"/>
+      <c r="G4" s="297"/>
+      <c r="H4" s="298"/>
       <c r="I4" s="28"/>
-      <c r="J4" s="269" t="s">
+      <c r="J4" s="299" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="270"/>
-      <c r="L4" s="270"/>
-      <c r="M4" s="270"/>
-      <c r="N4" s="270"/>
-      <c r="O4" s="270"/>
-      <c r="P4" s="270"/>
-      <c r="Q4" s="270"/>
-      <c r="R4" s="270"/>
-      <c r="S4" s="271"/>
+      <c r="K4" s="300"/>
+      <c r="L4" s="300"/>
+      <c r="M4" s="300"/>
+      <c r="N4" s="300"/>
+      <c r="O4" s="300"/>
+      <c r="P4" s="300"/>
+      <c r="Q4" s="300"/>
+      <c r="R4" s="300"/>
+      <c r="S4" s="301"/>
     </row>
     <row r="5" spans="1:20" s="29" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="30"/>
@@ -4881,7 +4878,7 @@
       <c r="R5" s="34"/>
       <c r="S5" s="45"/>
     </row>
-    <row r="6" spans="1:20" s="29" customFormat="1" ht="78">
+    <row r="6" spans="1:20" s="29" customFormat="1" ht="58.5">
       <c r="A6" s="36" t="s">
         <v>5</v>
       </c>
@@ -4914,7 +4911,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M6" s="41" t="s">
         <v>29</v>
@@ -4943,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="132" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="133">
         <v>10</v>
@@ -5008,24 +5005,24 @@
         <v>2</v>
       </c>
       <c r="B8" s="132" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="133">
         <v>19</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E8" s="133">
         <f t="shared" ref="E8:E55" si="8">D8*C8</f>
-        <v>190</v>
+        <v>950</v>
       </c>
       <c r="F8" s="135">
         <v>97.5</v>
       </c>
       <c r="G8" s="136">
         <f t="shared" si="0"/>
-        <v>9.75</v>
+        <v>1.95</v>
       </c>
       <c r="H8" s="137">
         <f t="shared" si="1"/>
@@ -5034,7 +5031,7 @@
       <c r="I8" s="173"/>
       <c r="J8" s="139">
         <f t="shared" ref="J8:J55" si="9">G8/$Q$2</f>
-        <v>2.9563371740448758</v>
+        <v>0.59126743480897515</v>
       </c>
       <c r="K8" s="139">
         <f t="shared" si="2"/>
@@ -5042,7 +5039,7 @@
       </c>
       <c r="L8" s="139">
         <f t="shared" si="3"/>
-        <v>3.2650375596945809</v>
+        <v>0.65300751193891615</v>
       </c>
       <c r="M8" s="139">
         <f t="shared" ref="M8:M55" si="10">L8*E8</f>
@@ -5055,7 +5052,7 @@
       </c>
       <c r="P8" s="141">
         <f t="shared" si="5"/>
-        <v>-3.2650375596945809</v>
+        <v>-0.65300751193891615</v>
       </c>
       <c r="Q8" s="141">
         <f t="shared" si="6"/>
@@ -5073,24 +5070,24 @@
         <v>3</v>
       </c>
       <c r="B9" s="174" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="133">
         <v>19</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="133">
         <f t="shared" si="8"/>
-        <v>190</v>
+        <v>912</v>
       </c>
       <c r="F9" s="135">
         <v>96</v>
       </c>
       <c r="G9" s="136">
         <f t="shared" si="0"/>
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="H9" s="137">
         <f t="shared" si="1"/>
@@ -5099,7 +5096,7 @@
       <c r="I9" s="173"/>
       <c r="J9" s="139">
         <f t="shared" si="9"/>
-        <v>2.9108550636749544</v>
+        <v>0.60642813826561548</v>
       </c>
       <c r="K9" s="139">
         <f t="shared" si="2"/>
@@ -5107,11 +5104,11 @@
       </c>
       <c r="L9" s="139">
         <f t="shared" si="3"/>
-        <v>3.214806212622356</v>
+        <v>0.66975129429632418</v>
       </c>
       <c r="M9" s="139">
         <f t="shared" si="10"/>
-        <v>610.8131803982476</v>
+        <v>610.81318039824771</v>
       </c>
       <c r="N9" s="140"/>
       <c r="O9" s="141">
@@ -5120,11 +5117,11 @@
       </c>
       <c r="P9" s="141">
         <f t="shared" si="5"/>
-        <v>-3.214806212622356</v>
+        <v>-0.66975129429632418</v>
       </c>
       <c r="Q9" s="141">
         <f t="shared" si="6"/>
-        <v>-610.8131803982476</v>
+        <v>-610.81318039824771</v>
       </c>
       <c r="R9" s="142" t="e">
         <f t="shared" si="7"/>
@@ -5138,13 +5135,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="174" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="133">
         <v>2</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="133">
         <f t="shared" si="8"/>
@@ -5203,7 +5200,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="174" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="133">
         <v>20</v>
@@ -5270,7 +5267,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="174" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="133">
         <v>10</v>
@@ -5337,7 +5334,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="174" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="133">
         <v>20</v>
@@ -5404,7 +5401,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="174" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="133">
         <v>30</v>
@@ -5471,7 +5468,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="133">
         <v>20</v>
@@ -5539,7 +5536,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="174" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="133">
         <v>20</v>
@@ -5607,7 +5604,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="174" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="133">
         <v>20</v>
@@ -5675,7 +5672,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="174" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" s="133">
         <v>19</v>
@@ -5733,7 +5730,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S18" s="143" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T18" s="144"/>
     </row>
@@ -5742,7 +5739,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" s="133">
         <v>20</v>
@@ -5809,7 +5806,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="133">
         <v>20</v>
@@ -5876,7 +5873,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C21" s="133">
         <v>20</v>
@@ -5943,7 +5940,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="133">
         <v>20</v>
@@ -6010,7 +6007,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="133">
         <v>20</v>
@@ -6077,7 +6074,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="133">
         <v>20</v>
@@ -6144,7 +6141,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="174" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" s="133">
         <v>15</v>
@@ -6197,13 +6194,13 @@
         <v>20</v>
       </c>
       <c r="B26" s="207" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="67">
         <v>19</v>
       </c>
       <c r="D26" s="89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" s="74">
         <f t="shared" ref="E26:E31" si="37">D26*C26</f>
@@ -6263,13 +6260,13 @@
         <v>21</v>
       </c>
       <c r="B27" s="207" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="67">
         <v>19</v>
       </c>
       <c r="D27" s="89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" s="74">
         <f t="shared" si="37"/>
@@ -6329,7 +6326,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="67">
         <v>19</v>
@@ -6396,7 +6393,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="67">
         <v>19</v>
@@ -6463,7 +6460,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="67">
         <v>19</v>
@@ -6527,13 +6524,13 @@
         <v>25</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" s="67">
         <v>10</v>
       </c>
       <c r="D31" s="89" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31" s="90">
         <f t="shared" si="37"/>
@@ -6591,7 +6588,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="174" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" s="133">
         <v>28</v>
@@ -6656,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="174" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" s="133">
         <v>20</v>
@@ -6721,7 +6718,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="174" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" s="133">
         <v>20</v>
@@ -6788,7 +6785,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="174" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="133">
         <v>20</v>
@@ -6856,7 +6853,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="174" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" s="133">
         <v>30</v>
@@ -6924,7 +6921,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="174" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C37" s="133">
         <v>20</v>
@@ -6985,7 +6982,7 @@
         <v>0.4839194193394436</v>
       </c>
       <c r="S37" s="143" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T37" s="144"/>
     </row>
@@ -6994,7 +6991,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="174" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C38" s="133">
         <v>20</v>
@@ -7055,7 +7052,7 @@
         <v>0.4839194193394436</v>
       </c>
       <c r="S38" s="143" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T38" s="144"/>
     </row>
@@ -7064,7 +7061,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="174" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="133">
         <v>40</v>
@@ -7125,7 +7122,7 @@
         <v>0.4839194193394436</v>
       </c>
       <c r="S39" s="143" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T39" s="144"/>
     </row>
@@ -7134,13 +7131,13 @@
         <v>34</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="74">
         <v>20</v>
       </c>
       <c r="D40" s="75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" s="74">
         <f>D40*C40</f>
@@ -7200,13 +7197,13 @@
         <v>35</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="74">
         <v>25</v>
       </c>
       <c r="D41" s="75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E41" s="74">
         <f t="shared" ref="E41:E50" si="56">D41*C41</f>
@@ -7266,13 +7263,13 @@
         <v>36</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="74">
         <v>30</v>
       </c>
       <c r="D42" s="75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E42" s="74">
         <f t="shared" si="56"/>
@@ -7332,13 +7329,13 @@
         <v>37</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C43" s="74">
         <v>20</v>
       </c>
       <c r="D43" s="75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E43" s="74">
         <f t="shared" si="56"/>
@@ -7398,7 +7395,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="146" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" s="3">
         <v>30</v>
@@ -7459,7 +7456,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7467,7 +7464,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="146" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C45" s="3">
         <v>30</v>
@@ -7528,7 +7525,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7536,7 +7533,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="146" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C46" s="3">
         <v>60</v>
@@ -7596,7 +7593,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7604,7 +7601,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="146" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="3">
         <v>50</v>
@@ -7664,7 +7661,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7672,7 +7669,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="146" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="3">
         <v>40</v>
@@ -7732,7 +7729,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:20" s="84" customFormat="1" ht="45" customHeight="1">
@@ -7740,13 +7737,13 @@
         <v>43</v>
       </c>
       <c r="B49" s="85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C49" s="74">
         <v>30</v>
       </c>
       <c r="D49" s="75" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E49" s="74">
         <f t="shared" si="56"/>
@@ -7800,7 +7797,7 @@
         <v>0.33906122273389055</v>
       </c>
       <c r="S49" s="145" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:20" s="84" customFormat="1" ht="45" customHeight="1">
@@ -7808,7 +7805,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C50" s="74">
         <v>30</v>
@@ -7875,7 +7872,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C51" s="74">
         <v>30</v>
@@ -7942,7 +7939,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C52" s="74">
         <v>50</v>
@@ -8009,7 +8006,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C53" s="74">
         <v>70</v>
@@ -8076,7 +8073,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="74">
         <v>60</v>
@@ -8143,13 +8140,13 @@
         <v>49</v>
       </c>
       <c r="B55" s="174" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" s="133">
         <v>10</v>
       </c>
       <c r="D55" s="134" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E55" s="133">
         <f t="shared" si="8"/>
@@ -8203,21 +8200,21 @@
         <v>0.28559861941725412</v>
       </c>
       <c r="S55" s="143" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T55" s="144"/>
     </row>
     <row r="56" spans="1:20" s="29" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A56" s="272"/>
-      <c r="B56" s="273"/>
-      <c r="C56" s="273"/>
-      <c r="D56" s="274"/>
+      <c r="A56" s="271"/>
+      <c r="B56" s="272"/>
+      <c r="C56" s="272"/>
+      <c r="D56" s="273"/>
       <c r="E56" s="178"/>
       <c r="F56" s="179"/>
-      <c r="G56" s="282" t="s">
+      <c r="G56" s="281" t="s">
         <v>15</v>
       </c>
-      <c r="H56" s="284">
+      <c r="H56" s="283">
         <f>SUM(H7:H55)</f>
         <v>114355.97999999997</v>
       </c>
@@ -8229,35 +8226,35 @@
         <f>SUM(K7:K55)</f>
         <v>34674.342025469974</v>
       </c>
-      <c r="L56" s="286" t="s">
+      <c r="L56" s="285" t="s">
         <v>17</v>
       </c>
-      <c r="M56" s="287"/>
-      <c r="N56" s="288">
+      <c r="M56" s="286"/>
+      <c r="N56" s="287">
         <f>SUM(O7:O55)</f>
         <v>48931</v>
       </c>
-      <c r="O56" s="289"/>
-      <c r="P56" s="298" t="s">
+      <c r="O56" s="288"/>
+      <c r="P56" s="267" t="s">
         <v>18</v>
       </c>
-      <c r="Q56" s="299"/>
-      <c r="R56" s="290">
+      <c r="Q56" s="268"/>
+      <c r="R56" s="259">
         <f>SUM(Q7:Q55)</f>
-        <v>11414.553071857192</v>
+        <v>11414.55307185719</v>
       </c>
       <c r="S56" s="183"/>
       <c r="T56" s="47"/>
     </row>
     <row r="57" spans="1:20" s="29" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A57" s="275"/>
-      <c r="B57" s="273"/>
-      <c r="C57" s="273"/>
-      <c r="D57" s="274"/>
+      <c r="A57" s="274"/>
+      <c r="B57" s="272"/>
+      <c r="C57" s="272"/>
+      <c r="D57" s="273"/>
       <c r="E57" s="178"/>
       <c r="F57" s="184"/>
-      <c r="G57" s="283"/>
-      <c r="H57" s="285"/>
+      <c r="G57" s="282"/>
+      <c r="H57" s="284"/>
       <c r="I57" s="185"/>
       <c r="J57" s="186" t="s">
         <v>33</v>
@@ -8266,21 +8263,21 @@
         <f>K56*0.09</f>
         <v>3120.6907822922976</v>
       </c>
-      <c r="L57" s="292"/>
-      <c r="M57" s="292"/>
-      <c r="N57" s="292"/>
-      <c r="O57" s="292"/>
-      <c r="P57" s="300"/>
-      <c r="Q57" s="301"/>
-      <c r="R57" s="291"/>
+      <c r="L57" s="261"/>
+      <c r="M57" s="261"/>
+      <c r="N57" s="261"/>
+      <c r="O57" s="261"/>
+      <c r="P57" s="269"/>
+      <c r="Q57" s="270"/>
+      <c r="R57" s="260"/>
       <c r="S57" s="188"/>
       <c r="T57" s="47"/>
     </row>
     <row r="58" spans="1:20" s="29" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A58" s="276"/>
-      <c r="B58" s="277"/>
-      <c r="C58" s="277"/>
-      <c r="D58" s="278"/>
+      <c r="A58" s="275"/>
+      <c r="B58" s="276"/>
+      <c r="C58" s="276"/>
+      <c r="D58" s="277"/>
       <c r="E58" s="189"/>
       <c r="F58" s="190"/>
       <c r="G58" s="191" t="s">
@@ -8297,26 +8294,26 @@
         <f>1650/3.3</f>
         <v>500</v>
       </c>
-      <c r="L58" s="292"/>
-      <c r="M58" s="292"/>
-      <c r="N58" s="292"/>
-      <c r="O58" s="292"/>
-      <c r="P58" s="293" t="s">
+      <c r="L58" s="261"/>
+      <c r="M58" s="261"/>
+      <c r="N58" s="261"/>
+      <c r="O58" s="261"/>
+      <c r="P58" s="262" t="s">
         <v>21</v>
       </c>
-      <c r="Q58" s="294"/>
+      <c r="Q58" s="263"/>
       <c r="R58" s="195">
         <f>R56/N56</f>
-        <v>0.23327855698549368</v>
+        <v>0.23327855698549366</v>
       </c>
       <c r="S58" s="196"/>
       <c r="T58" s="47"/>
     </row>
     <row r="59" spans="1:20" s="29" customFormat="1" ht="48" thickBot="1">
-      <c r="A59" s="279"/>
-      <c r="B59" s="280"/>
-      <c r="C59" s="280"/>
-      <c r="D59" s="281"/>
+      <c r="A59" s="278"/>
+      <c r="B59" s="279"/>
+      <c r="C59" s="279"/>
+      <c r="D59" s="280"/>
       <c r="E59" s="197"/>
       <c r="F59" s="198"/>
       <c r="G59" s="199" t="s">
@@ -8337,11 +8334,11 @@
       <c r="L59" s="203" t="s">
         <v>23</v>
       </c>
-      <c r="M59" s="295">
+      <c r="M59" s="264">
         <f>K58/K56</f>
         <v>1.4419884294638552E-2</v>
       </c>
-      <c r="N59" s="296"/>
+      <c r="N59" s="265"/>
       <c r="O59" s="204"/>
       <c r="P59" s="205"/>
       <c r="Q59" s="205"/>
@@ -8380,11 +8377,11 @@
       <c r="G61" s="157"/>
       <c r="H61" s="158"/>
       <c r="I61" s="151"/>
-      <c r="J61" s="297"/>
-      <c r="K61" s="297"/>
-      <c r="L61" s="297"/>
-      <c r="M61" s="297"/>
-      <c r="N61" s="297"/>
+      <c r="J61" s="266"/>
+      <c r="K61" s="266"/>
+      <c r="L61" s="266"/>
+      <c r="M61" s="266"/>
+      <c r="N61" s="266"/>
       <c r="O61" s="154"/>
       <c r="P61" s="154"/>
       <c r="Q61" s="154"/>
@@ -8414,7 +8411,7 @@
     </row>
     <row r="63" spans="1:20" ht="15.75" customHeight="1">
       <c r="A63" s="163" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" s="211"/>
       <c r="C63" s="154"/>
@@ -8437,7 +8434,7 @@
     </row>
     <row r="64" spans="1:20" ht="18" customHeight="1">
       <c r="A64" s="163" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B64" s="211"/>
       <c r="C64" s="154"/>
@@ -8482,23 +8479,23 @@
   </sheetData>
   <autoFilter ref="B6:Q6" xr:uid="{90601705-1B33-409B-B71E-3AEEAC21DCA1}"/>
   <mergeCells count="17">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="J4:S4"/>
+    <mergeCell ref="A56:D59"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="N56:O56"/>
     <mergeCell ref="R56:R57"/>
     <mergeCell ref="L57:O58"/>
     <mergeCell ref="P58:Q58"/>
     <mergeCell ref="M59:N59"/>
     <mergeCell ref="J61:N61"/>
     <mergeCell ref="P56:Q57"/>
-    <mergeCell ref="A56:D59"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="J4:S4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/retail/rpoc/assets/files/9 .JB YAP BROTHERS FOOD SDN BHD - JULY'25.xlsx
+++ b/retail/rpoc/assets/files/9 .JB YAP BROTHERS FOOD SDN BHD - JULY'25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\Desktop\SEPT PROFIT LISTING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E31E87-7C05-4781-AA25-524E41707823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286B9648-A96E-47DE-9A9C-4EB78F6CDD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="588" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="588" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25-11590" sheetId="12" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="109">
   <si>
     <t>Tian Ma Group Holdings Pte Ltd</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>48</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>1 for $2.50
@@ -2230,6 +2233,96 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2278,94 +2371,97 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="2" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2402,99 +2498,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="3" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4343,50 +4346,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="32.450000000000003" customHeight="1">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="243" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="214"/>
-      <c r="L1" s="214"/>
-      <c r="M1" s="214"/>
-      <c r="N1" s="214"/>
-      <c r="O1" s="215"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="244"/>
+      <c r="D1" s="244"/>
+      <c r="E1" s="244"/>
+      <c r="F1" s="244"/>
+      <c r="G1" s="244"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="244"/>
+      <c r="L1" s="244"/>
+      <c r="M1" s="244"/>
+      <c r="N1" s="244"/>
+      <c r="O1" s="245"/>
       <c r="P1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="216" t="s">
-        <v>52</v>
-      </c>
-      <c r="R1" s="216"/>
+      <c r="Q1" s="246" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="246"/>
       <c r="S1" s="51"/>
     </row>
     <row r="2" spans="1:19" ht="31.7" customHeight="1" thickBot="1">
-      <c r="A2" s="217" t="s">
+      <c r="A2" s="247" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="219"/>
+      <c r="B2" s="248"/>
+      <c r="C2" s="248"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="248"/>
+      <c r="N2" s="248"/>
+      <c r="O2" s="249"/>
       <c r="P2" s="16" t="s">
         <v>2</v>
       </c>
@@ -4414,37 +4417,37 @@
       <c r="M3" s="26"/>
       <c r="N3" s="27"/>
       <c r="O3" s="26"/>
-      <c r="P3" s="220" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="221"/>
-      <c r="S3" s="222"/>
+      <c r="P3" s="250" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="252"/>
     </row>
     <row r="4" spans="1:19" ht="22.7" customHeight="1" thickBot="1">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="253" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="224"/>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="225"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="255"/>
       <c r="I4" s="53"/>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="256" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="227"/>
-      <c r="L4" s="227"/>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="228"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
+      <c r="M4" s="257"/>
+      <c r="N4" s="257"/>
+      <c r="O4" s="257"/>
+      <c r="P4" s="257"/>
+      <c r="Q4" s="257"/>
+      <c r="R4" s="257"/>
+      <c r="S4" s="258"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="21"/>
@@ -4500,7 +4503,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M6" s="64" t="s">
         <v>29</v>
@@ -4525,16 +4528,16 @@
       </c>
     </row>
     <row r="68" spans="1:19" ht="48" customHeight="1" thickBot="1">
-      <c r="A68" s="239"/>
-      <c r="B68" s="240"/>
-      <c r="C68" s="240"/>
-      <c r="D68" s="241"/>
+      <c r="A68" s="223"/>
+      <c r="B68" s="224"/>
+      <c r="C68" s="224"/>
+      <c r="D68" s="225"/>
       <c r="E68" s="93"/>
       <c r="F68" s="125"/>
-      <c r="G68" s="249" t="s">
+      <c r="G68" s="233" t="s">
         <v>15</v>
       </c>
-      <c r="H68" s="251">
+      <c r="H68" s="235">
         <f>SUM([1]Sheet3!H306:H366)</f>
         <v>113452.4</v>
       </c>
@@ -4546,34 +4549,34 @@
         <f>SUM([1]Sheet3!K314:K366)</f>
         <v>30864.464831804271</v>
       </c>
-      <c r="L68" s="253" t="s">
+      <c r="L68" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="254"/>
-      <c r="N68" s="255">
+      <c r="M68" s="238"/>
+      <c r="N68" s="239">
         <f>SUM([1]Sheet3!O314:O366)</f>
         <v>55517.599999999999</v>
       </c>
-      <c r="O68" s="256"/>
-      <c r="P68" s="234" t="s">
+      <c r="O68" s="240"/>
+      <c r="P68" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="Q68" s="235"/>
-      <c r="R68" s="257">
+      <c r="Q68" s="219"/>
+      <c r="R68" s="241">
         <f>N68-K71</f>
         <v>21373.813576494438</v>
       </c>
       <c r="S68" s="97"/>
     </row>
     <row r="69" spans="1:19" ht="48" customHeight="1" thickBot="1">
-      <c r="A69" s="242"/>
-      <c r="B69" s="240"/>
-      <c r="C69" s="240"/>
-      <c r="D69" s="241"/>
+      <c r="A69" s="226"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
+      <c r="D69" s="225"/>
       <c r="E69" s="93"/>
       <c r="F69" s="126"/>
-      <c r="G69" s="250"/>
-      <c r="H69" s="252"/>
+      <c r="G69" s="234"/>
+      <c r="H69" s="236"/>
       <c r="I69" s="98"/>
       <c r="J69" s="99" t="s">
         <v>33</v>
@@ -4582,20 +4585,20 @@
         <f>K68*0.09</f>
         <v>2777.8018348623841</v>
       </c>
-      <c r="L69" s="229"/>
-      <c r="M69" s="229"/>
-      <c r="N69" s="229"/>
-      <c r="O69" s="229"/>
-      <c r="P69" s="236"/>
-      <c r="Q69" s="237"/>
-      <c r="R69" s="258"/>
+      <c r="L69" s="213"/>
+      <c r="M69" s="213"/>
+      <c r="N69" s="213"/>
+      <c r="O69" s="213"/>
+      <c r="P69" s="220"/>
+      <c r="Q69" s="221"/>
+      <c r="R69" s="242"/>
       <c r="S69" s="101"/>
     </row>
     <row r="70" spans="1:19" ht="70.5" thickBot="1">
-      <c r="A70" s="243"/>
-      <c r="B70" s="244"/>
-      <c r="C70" s="244"/>
-      <c r="D70" s="245"/>
+      <c r="A70" s="227"/>
+      <c r="B70" s="228"/>
+      <c r="C70" s="228"/>
+      <c r="D70" s="229"/>
       <c r="E70" s="102"/>
       <c r="F70" s="127"/>
       <c r="G70" s="103" t="s">
@@ -4612,14 +4615,14 @@
         <f>1650/3.29</f>
         <v>501.51975683890578</v>
       </c>
-      <c r="L70" s="229"/>
-      <c r="M70" s="229"/>
-      <c r="N70" s="229"/>
-      <c r="O70" s="229"/>
-      <c r="P70" s="230" t="s">
+      <c r="L70" s="213"/>
+      <c r="M70" s="213"/>
+      <c r="N70" s="213"/>
+      <c r="O70" s="213"/>
+      <c r="P70" s="214" t="s">
         <v>21</v>
       </c>
-      <c r="Q70" s="231"/>
+      <c r="Q70" s="215"/>
       <c r="R70" s="107">
         <f>R68/N68</f>
         <v>0.38499167068631279</v>
@@ -4627,10 +4630,10 @@
       <c r="S70" s="108"/>
     </row>
     <row r="71" spans="1:19" ht="93.75" thickBot="1">
-      <c r="A71" s="246"/>
-      <c r="B71" s="247"/>
-      <c r="C71" s="247"/>
-      <c r="D71" s="248"/>
+      <c r="A71" s="230"/>
+      <c r="B71" s="231"/>
+      <c r="C71" s="231"/>
+      <c r="D71" s="232"/>
       <c r="E71" s="109"/>
       <c r="F71" s="128"/>
       <c r="G71" s="110" t="s">
@@ -4651,11 +4654,11 @@
       <c r="L71" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="M71" s="232">
+      <c r="M71" s="216">
         <f>K70/K68</f>
         <v>1.624909939543533E-2</v>
       </c>
-      <c r="N71" s="233"/>
+      <c r="N71" s="217"/>
       <c r="O71" s="115"/>
       <c r="P71" s="24"/>
       <c r="Q71" s="24"/>
@@ -4679,14 +4682,14 @@
     </row>
     <row r="77" spans="1:19" s="117" customFormat="1">
       <c r="A77" s="117" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F77" s="130"/>
       <c r="N77" s="118"/>
     </row>
-    <row r="78" spans="1:19" s="238" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A78" s="238" t="s">
-        <v>51</v>
+    <row r="78" spans="1:19" s="222" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A78" s="222" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:19" s="117" customFormat="1">
@@ -4702,6 +4705,12 @@
   </sheetData>
   <autoFilter ref="A6:T71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="17">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="J4:S4"/>
     <mergeCell ref="L69:O70"/>
     <mergeCell ref="P70:Q70"/>
     <mergeCell ref="M71:N71"/>
@@ -4713,12 +4722,6 @@
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="N68:O68"/>
     <mergeCell ref="R68:R69"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="J4:S4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4735,10 +4738,10 @@
     <col min="2" max="2" width="65.28515625" style="47" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" style="1" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="2.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" bestFit="1" customWidth="1"/>
@@ -4754,50 +4757,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" ht="32.450000000000003" customHeight="1">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="259" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="290"/>
-      <c r="C1" s="290"/>
-      <c r="D1" s="290"/>
-      <c r="E1" s="290"/>
-      <c r="F1" s="290"/>
-      <c r="G1" s="290"/>
-      <c r="H1" s="290"/>
-      <c r="I1" s="290"/>
-      <c r="J1" s="290"/>
-      <c r="K1" s="290"/>
-      <c r="L1" s="290"/>
-      <c r="M1" s="290"/>
-      <c r="N1" s="290"/>
-      <c r="O1" s="291"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
+      <c r="N1" s="260"/>
+      <c r="O1" s="261"/>
       <c r="P1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="292">
+      <c r="Q1" s="262">
         <v>45738</v>
       </c>
-      <c r="R1" s="292"/>
+      <c r="R1" s="262"/>
       <c r="S1" s="44"/>
     </row>
     <row r="2" spans="1:20" s="20" customFormat="1" ht="31.7" customHeight="1" thickBot="1">
-      <c r="A2" s="217" t="s">
+      <c r="A2" s="247" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="219"/>
+      <c r="B2" s="248"/>
+      <c r="C2" s="248"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="248"/>
+      <c r="N2" s="248"/>
+      <c r="O2" s="249"/>
       <c r="P2" s="16" t="s">
         <v>2</v>
       </c>
@@ -4825,37 +4828,37 @@
       <c r="M3" s="26"/>
       <c r="N3" s="27"/>
       <c r="O3" s="26"/>
-      <c r="P3" s="293" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="294"/>
-      <c r="R3" s="294"/>
-      <c r="S3" s="295"/>
+      <c r="P3" s="263" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q3" s="264"/>
+      <c r="R3" s="264"/>
+      <c r="S3" s="265"/>
     </row>
     <row r="4" spans="1:20" s="29" customFormat="1" ht="22.7" customHeight="1" thickBot="1">
-      <c r="A4" s="296" t="s">
+      <c r="A4" s="266" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="297"/>
-      <c r="C4" s="297"/>
-      <c r="D4" s="297"/>
-      <c r="E4" s="297"/>
-      <c r="F4" s="297"/>
-      <c r="G4" s="297"/>
-      <c r="H4" s="298"/>
+      <c r="B4" s="267"/>
+      <c r="C4" s="267"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="268"/>
       <c r="I4" s="28"/>
-      <c r="J4" s="299" t="s">
+      <c r="J4" s="269" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="300"/>
-      <c r="L4" s="300"/>
-      <c r="M4" s="300"/>
-      <c r="N4" s="300"/>
-      <c r="O4" s="300"/>
-      <c r="P4" s="300"/>
-      <c r="Q4" s="300"/>
-      <c r="R4" s="300"/>
-      <c r="S4" s="301"/>
+      <c r="K4" s="270"/>
+      <c r="L4" s="270"/>
+      <c r="M4" s="270"/>
+      <c r="N4" s="270"/>
+      <c r="O4" s="270"/>
+      <c r="P4" s="270"/>
+      <c r="Q4" s="270"/>
+      <c r="R4" s="270"/>
+      <c r="S4" s="271"/>
     </row>
     <row r="5" spans="1:20" s="29" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="30"/>
@@ -4878,7 +4881,7 @@
       <c r="R5" s="34"/>
       <c r="S5" s="45"/>
     </row>
-    <row r="6" spans="1:20" s="29" customFormat="1" ht="58.5">
+    <row r="6" spans="1:20" s="29" customFormat="1" ht="78">
       <c r="A6" s="36" t="s">
         <v>5</v>
       </c>
@@ -4911,7 +4914,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M6" s="41" t="s">
         <v>29</v>
@@ -4940,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="132" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="133">
         <v>10</v>
@@ -5005,24 +5008,24 @@
         <v>2</v>
       </c>
       <c r="B8" s="132" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="133">
         <v>19</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E8" s="133">
         <f t="shared" ref="E8:E55" si="8">D8*C8</f>
-        <v>950</v>
+        <v>190</v>
       </c>
       <c r="F8" s="135">
         <v>97.5</v>
       </c>
       <c r="G8" s="136">
         <f t="shared" si="0"/>
-        <v>1.95</v>
+        <v>9.75</v>
       </c>
       <c r="H8" s="137">
         <f t="shared" si="1"/>
@@ -5031,7 +5034,7 @@
       <c r="I8" s="173"/>
       <c r="J8" s="139">
         <f t="shared" ref="J8:J55" si="9">G8/$Q$2</f>
-        <v>0.59126743480897515</v>
+        <v>2.9563371740448758</v>
       </c>
       <c r="K8" s="139">
         <f t="shared" si="2"/>
@@ -5039,7 +5042,7 @@
       </c>
       <c r="L8" s="139">
         <f t="shared" si="3"/>
-        <v>0.65300751193891615</v>
+        <v>3.2650375596945809</v>
       </c>
       <c r="M8" s="139">
         <f t="shared" ref="M8:M55" si="10">L8*E8</f>
@@ -5052,7 +5055,7 @@
       </c>
       <c r="P8" s="141">
         <f t="shared" si="5"/>
-        <v>-0.65300751193891615</v>
+        <v>-3.2650375596945809</v>
       </c>
       <c r="Q8" s="141">
         <f t="shared" si="6"/>
@@ -5070,24 +5073,24 @@
         <v>3</v>
       </c>
       <c r="B9" s="174" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" s="133">
         <v>19</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="133">
         <f t="shared" si="8"/>
-        <v>912</v>
+        <v>190</v>
       </c>
       <c r="F9" s="135">
         <v>96</v>
       </c>
       <c r="G9" s="136">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>9.6</v>
       </c>
       <c r="H9" s="137">
         <f t="shared" si="1"/>
@@ -5096,7 +5099,7 @@
       <c r="I9" s="173"/>
       <c r="J9" s="139">
         <f t="shared" si="9"/>
-        <v>0.60642813826561548</v>
+        <v>2.9108550636749544</v>
       </c>
       <c r="K9" s="139">
         <f t="shared" si="2"/>
@@ -5104,11 +5107,11 @@
       </c>
       <c r="L9" s="139">
         <f t="shared" si="3"/>
-        <v>0.66975129429632418</v>
+        <v>3.214806212622356</v>
       </c>
       <c r="M9" s="139">
         <f t="shared" si="10"/>
-        <v>610.81318039824771</v>
+        <v>610.8131803982476</v>
       </c>
       <c r="N9" s="140"/>
       <c r="O9" s="141">
@@ -5117,11 +5120,11 @@
       </c>
       <c r="P9" s="141">
         <f t="shared" si="5"/>
-        <v>-0.66975129429632418</v>
+        <v>-3.214806212622356</v>
       </c>
       <c r="Q9" s="141">
         <f t="shared" si="6"/>
-        <v>-610.81318039824771</v>
+        <v>-610.8131803982476</v>
       </c>
       <c r="R9" s="142" t="e">
         <f t="shared" si="7"/>
@@ -5135,13 +5138,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="174" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="133">
         <v>2</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="133">
         <f t="shared" si="8"/>
@@ -5200,7 +5203,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="174" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="133">
         <v>20</v>
@@ -5267,7 +5270,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="174" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="133">
         <v>10</v>
@@ -5334,7 +5337,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="174" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="133">
         <v>20</v>
@@ -5401,7 +5404,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="174" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" s="133">
         <v>30</v>
@@ -5468,7 +5471,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="133">
         <v>20</v>
@@ -5536,7 +5539,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="174" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="133">
         <v>20</v>
@@ -5604,7 +5607,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="174" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="133">
         <v>20</v>
@@ -5672,7 +5675,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="174" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" s="133">
         <v>19</v>
@@ -5730,7 +5733,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S18" s="143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T18" s="144"/>
     </row>
@@ -5739,7 +5742,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="133">
         <v>20</v>
@@ -5806,7 +5809,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" s="133">
         <v>20</v>
@@ -5873,7 +5876,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" s="133">
         <v>20</v>
@@ -5940,7 +5943,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="133">
         <v>20</v>
@@ -6007,7 +6010,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" s="133">
         <v>20</v>
@@ -6074,7 +6077,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" s="133">
         <v>20</v>
@@ -6141,7 +6144,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="174" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" s="133">
         <v>15</v>
@@ -6194,13 +6197,13 @@
         <v>20</v>
       </c>
       <c r="B26" s="207" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="67">
         <v>19</v>
       </c>
       <c r="D26" s="89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" s="74">
         <f t="shared" ref="E26:E31" si="37">D26*C26</f>
@@ -6260,13 +6263,13 @@
         <v>21</v>
       </c>
       <c r="B27" s="207" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" s="67">
         <v>19</v>
       </c>
       <c r="D27" s="89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" s="74">
         <f t="shared" si="37"/>
@@ -6326,7 +6329,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="67">
         <v>19</v>
@@ -6393,7 +6396,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" s="67">
         <v>19</v>
@@ -6460,7 +6463,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="67">
         <v>19</v>
@@ -6524,13 +6527,13 @@
         <v>25</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" s="67">
         <v>10</v>
       </c>
       <c r="D31" s="89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="90">
         <f t="shared" si="37"/>
@@ -6588,7 +6591,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="174" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C32" s="133">
         <v>28</v>
@@ -6653,7 +6656,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="174" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" s="133">
         <v>20</v>
@@ -6718,7 +6721,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="174" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" s="133">
         <v>20</v>
@@ -6785,7 +6788,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="174" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C35" s="133">
         <v>20</v>
@@ -6853,7 +6856,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="174" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36" s="133">
         <v>30</v>
@@ -6921,7 +6924,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="174" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C37" s="133">
         <v>20</v>
@@ -6982,7 +6985,7 @@
         <v>0.4839194193394436</v>
       </c>
       <c r="S37" s="143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T37" s="144"/>
     </row>
@@ -6991,7 +6994,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="174" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C38" s="133">
         <v>20</v>
@@ -7052,7 +7055,7 @@
         <v>0.4839194193394436</v>
       </c>
       <c r="S38" s="143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T38" s="144"/>
     </row>
@@ -7061,7 +7064,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="174" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C39" s="133">
         <v>40</v>
@@ -7122,7 +7125,7 @@
         <v>0.4839194193394436</v>
       </c>
       <c r="S39" s="143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T39" s="144"/>
     </row>
@@ -7131,13 +7134,13 @@
         <v>34</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C40" s="74">
         <v>20</v>
       </c>
       <c r="D40" s="75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E40" s="74">
         <f>D40*C40</f>
@@ -7197,13 +7200,13 @@
         <v>35</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C41" s="74">
         <v>25</v>
       </c>
       <c r="D41" s="75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E41" s="74">
         <f t="shared" ref="E41:E50" si="56">D41*C41</f>
@@ -7263,13 +7266,13 @@
         <v>36</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C42" s="74">
         <v>30</v>
       </c>
       <c r="D42" s="75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42" s="74">
         <f t="shared" si="56"/>
@@ -7329,13 +7332,13 @@
         <v>37</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C43" s="74">
         <v>20</v>
       </c>
       <c r="D43" s="75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E43" s="74">
         <f t="shared" si="56"/>
@@ -7395,7 +7398,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="146" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="3">
         <v>30</v>
@@ -7456,7 +7459,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7464,7 +7467,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="146" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C45" s="3">
         <v>30</v>
@@ -7525,7 +7528,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7533,7 +7536,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="146" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" s="3">
         <v>60</v>
@@ -7593,7 +7596,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7601,7 +7604,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="146" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C47" s="3">
         <v>50</v>
@@ -7661,7 +7664,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:20" s="11" customFormat="1" ht="45" customHeight="1">
@@ -7669,7 +7672,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="146" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C48" s="3">
         <v>40</v>
@@ -7729,7 +7732,7 @@
         <v>0.27178499897239233</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:20" s="84" customFormat="1" ht="45" customHeight="1">
@@ -7737,13 +7740,13 @@
         <v>43</v>
       </c>
       <c r="B49" s="85" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C49" s="74">
         <v>30</v>
       </c>
       <c r="D49" s="75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E49" s="74">
         <f t="shared" si="56"/>
@@ -7797,7 +7800,7 @@
         <v>0.33906122273389055</v>
       </c>
       <c r="S49" s="145" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:20" s="84" customFormat="1" ht="45" customHeight="1">
@@ -7805,7 +7808,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" s="74">
         <v>30</v>
@@ -7872,7 +7875,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="73" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51" s="74">
         <v>30</v>
@@ -7939,7 +7942,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="73" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C52" s="74">
         <v>50</v>
@@ -8006,7 +8009,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C53" s="74">
         <v>70</v>
@@ -8073,7 +8076,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C54" s="74">
         <v>60</v>
@@ -8140,13 +8143,13 @@
         <v>49</v>
       </c>
       <c r="B55" s="174" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C55" s="133">
         <v>10</v>
       </c>
       <c r="D55" s="134" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E55" s="133">
         <f t="shared" si="8"/>
@@ -8200,21 +8203,21 @@
         <v>0.28559861941725412</v>
       </c>
       <c r="S55" s="143" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T55" s="144"/>
     </row>
     <row r="56" spans="1:20" s="29" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A56" s="271"/>
-      <c r="B56" s="272"/>
-      <c r="C56" s="272"/>
-      <c r="D56" s="273"/>
+      <c r="A56" s="272"/>
+      <c r="B56" s="273"/>
+      <c r="C56" s="273"/>
+      <c r="D56" s="274"/>
       <c r="E56" s="178"/>
       <c r="F56" s="179"/>
-      <c r="G56" s="281" t="s">
+      <c r="G56" s="282" t="s">
         <v>15</v>
       </c>
-      <c r="H56" s="283">
+      <c r="H56" s="284">
         <f>SUM(H7:H55)</f>
         <v>114355.97999999997</v>
       </c>
@@ -8226,35 +8229,35 @@
         <f>SUM(K7:K55)</f>
         <v>34674.342025469974</v>
       </c>
-      <c r="L56" s="285" t="s">
+      <c r="L56" s="286" t="s">
         <v>17</v>
       </c>
-      <c r="M56" s="286"/>
-      <c r="N56" s="287">
+      <c r="M56" s="287"/>
+      <c r="N56" s="288">
         <f>SUM(O7:O55)</f>
         <v>48931</v>
       </c>
-      <c r="O56" s="288"/>
-      <c r="P56" s="267" t="s">
+      <c r="O56" s="289"/>
+      <c r="P56" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="Q56" s="268"/>
-      <c r="R56" s="259">
+      <c r="Q56" s="299"/>
+      <c r="R56" s="290">
         <f>SUM(Q7:Q55)</f>
-        <v>11414.55307185719</v>
+        <v>11414.553071857192</v>
       </c>
       <c r="S56" s="183"/>
       <c r="T56" s="47"/>
     </row>
     <row r="57" spans="1:20" s="29" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A57" s="274"/>
-      <c r="B57" s="272"/>
-      <c r="C57" s="272"/>
-      <c r="D57" s="273"/>
+      <c r="A57" s="275"/>
+      <c r="B57" s="273"/>
+      <c r="C57" s="273"/>
+      <c r="D57" s="274"/>
       <c r="E57" s="178"/>
       <c r="F57" s="184"/>
-      <c r="G57" s="282"/>
-      <c r="H57" s="284"/>
+      <c r="G57" s="283"/>
+      <c r="H57" s="285"/>
       <c r="I57" s="185"/>
       <c r="J57" s="186" t="s">
         <v>33</v>
@@ -8263,21 +8266,21 @@
         <f>K56*0.09</f>
         <v>3120.6907822922976</v>
       </c>
-      <c r="L57" s="261"/>
-      <c r="M57" s="261"/>
-      <c r="N57" s="261"/>
-      <c r="O57" s="261"/>
-      <c r="P57" s="269"/>
-      <c r="Q57" s="270"/>
-      <c r="R57" s="260"/>
+      <c r="L57" s="292"/>
+      <c r="M57" s="292"/>
+      <c r="N57" s="292"/>
+      <c r="O57" s="292"/>
+      <c r="P57" s="300"/>
+      <c r="Q57" s="301"/>
+      <c r="R57" s="291"/>
       <c r="S57" s="188"/>
       <c r="T57" s="47"/>
     </row>
     <row r="58" spans="1:20" s="29" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A58" s="275"/>
-      <c r="B58" s="276"/>
-      <c r="C58" s="276"/>
-      <c r="D58" s="277"/>
+      <c r="A58" s="276"/>
+      <c r="B58" s="277"/>
+      <c r="C58" s="277"/>
+      <c r="D58" s="278"/>
       <c r="E58" s="189"/>
       <c r="F58" s="190"/>
       <c r="G58" s="191" t="s">
@@ -8294,26 +8297,26 @@
         <f>1650/3.3</f>
         <v>500</v>
       </c>
-      <c r="L58" s="261"/>
-      <c r="M58" s="261"/>
-      <c r="N58" s="261"/>
-      <c r="O58" s="261"/>
-      <c r="P58" s="262" t="s">
+      <c r="L58" s="292"/>
+      <c r="M58" s="292"/>
+      <c r="N58" s="292"/>
+      <c r="O58" s="292"/>
+      <c r="P58" s="293" t="s">
         <v>21</v>
       </c>
-      <c r="Q58" s="263"/>
+      <c r="Q58" s="294"/>
       <c r="R58" s="195">
         <f>R56/N56</f>
-        <v>0.23327855698549366</v>
+        <v>0.23327855698549368</v>
       </c>
       <c r="S58" s="196"/>
       <c r="T58" s="47"/>
     </row>
     <row r="59" spans="1:20" s="29" customFormat="1" ht="48" thickBot="1">
-      <c r="A59" s="278"/>
-      <c r="B59" s="279"/>
-      <c r="C59" s="279"/>
-      <c r="D59" s="280"/>
+      <c r="A59" s="279"/>
+      <c r="B59" s="280"/>
+      <c r="C59" s="280"/>
+      <c r="D59" s="281"/>
       <c r="E59" s="197"/>
       <c r="F59" s="198"/>
       <c r="G59" s="199" t="s">
@@ -8334,11 +8337,11 @@
       <c r="L59" s="203" t="s">
         <v>23</v>
       </c>
-      <c r="M59" s="264">
+      <c r="M59" s="295">
         <f>K58/K56</f>
         <v>1.4419884294638552E-2</v>
       </c>
-      <c r="N59" s="265"/>
+      <c r="N59" s="296"/>
       <c r="O59" s="204"/>
       <c r="P59" s="205"/>
       <c r="Q59" s="205"/>
@@ -8377,11 +8380,11 @@
       <c r="G61" s="157"/>
       <c r="H61" s="158"/>
       <c r="I61" s="151"/>
-      <c r="J61" s="266"/>
-      <c r="K61" s="266"/>
-      <c r="L61" s="266"/>
-      <c r="M61" s="266"/>
-      <c r="N61" s="266"/>
+      <c r="J61" s="297"/>
+      <c r="K61" s="297"/>
+      <c r="L61" s="297"/>
+      <c r="M61" s="297"/>
+      <c r="N61" s="297"/>
       <c r="O61" s="154"/>
       <c r="P61" s="154"/>
       <c r="Q61" s="154"/>
@@ -8411,7 +8414,7 @@
     </row>
     <row r="63" spans="1:20" ht="15.75" customHeight="1">
       <c r="A63" s="163" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B63" s="211"/>
       <c r="C63" s="154"/>
@@ -8434,7 +8437,7 @@
     </row>
     <row r="64" spans="1:20" ht="18" customHeight="1">
       <c r="A64" s="163" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B64" s="211"/>
       <c r="C64" s="154"/>
@@ -8479,23 +8482,23 @@
   </sheetData>
   <autoFilter ref="B6:Q6" xr:uid="{90601705-1B33-409B-B71E-3AEEAC21DCA1}"/>
   <mergeCells count="17">
+    <mergeCell ref="R56:R57"/>
+    <mergeCell ref="L57:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="J61:N61"/>
+    <mergeCell ref="P56:Q57"/>
+    <mergeCell ref="A56:D59"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="N56:O56"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="P3:S3"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="J4:S4"/>
-    <mergeCell ref="A56:D59"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="R56:R57"/>
-    <mergeCell ref="L57:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="J61:N61"/>
-    <mergeCell ref="P56:Q57"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
